--- a/Week1-day2-assignment.xlsx
+++ b/Week1-day2-assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prathb\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB1204-00F3-4F34-B509-45DB1B8831BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20384D9-BC3F-4E27-98E8-A73824C425C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25790AD6-3FE0-4516-917B-9DCF86749E0A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>Service providers</t>
   </si>
@@ -342,6 +342,230 @@
   </si>
   <si>
     <t>GPT-5.x (GPT-4o and mini, 4V)</t>
+  </si>
+  <si>
+    <t>import { chromium } from '@playwright/test';
+(async () =&gt; {
+  const browser = await chromium.launch({ headless: false });
+  const context = await browser.newContext();
+  const page = await context.newPage();
+  await page.goto('https://accounts.google.com');
+  // Enter email
+  await page.fill('input[type="email"]', 'your-email@gmail.com');
+  await page.click('#identifierNext');
+  // Enter password
+  await page.waitForSelector('input[type="password"]', { timeout: 60000 });
+  await page.fill('input[type="password"]', 'your-password');
+  await page.click('#passwordNext');
+  // ⛔ STOP HERE
+  // Complete 2FA MANUAL+A1LY (OTP / phone approval)
+  // Wait until Gmail loads
+  await page.waitForURL('https://mail.google.com/**', { timeout: 120000 });
+  // Save authenticated state
+  await context.storageState({ path: 'auth.json' });
+  await browser.close();
+})();</t>
+  </si>
+  <si>
+    <t>Prompt used: create a testscript in typescript for gmail login with two step authentication</t>
+  </si>
+  <si>
+    <t>import { test, expect } from '@playwright/test';
+import { authenticator } from 'otplib';
+// Replace with your test account credentials and TOTP secret
+const EMAIL = 'your-test@gmail.com';
+const PASSWORD = 'your-test-password';
+const TOTP_SECRET = 'YOUR_TOTP_SECRET_HERE'; // From Google Authenticator setup
+test('Login to Gmail with 2FA', async ({ page }) =&gt; {
+  // Step 1: Go to Gmail login
+  await page.goto('https://mail.google.com');
+  // Step 2: Enter email
+  await page.fill('input[type="email"]', EMAIL);
+  await page.click('button:has-text("Next")');
+  // Wait for password field (may take a moment)
+  await page.waitForSelector('input[type="password"]', { timeout: 10000 });
+  // Step 3: Enter password
+  await page.fill('input[type="password"]', PASSWORD);
+  await page.click('button:has-text("Next")');
+  // Step 4: Handle 2FA prompt
+  // Google may show "Try another way" – we assume TOTP is the primary method
+  await page.waitForSelector('input[type="tel"]', { timeout: 15000 });
+  // Generate TOTP code
+  const token = authenticator.generate(TOTP_SECRET);
+  console.log('Generated 2FA code:', token);
+  // Step 5: Enter 2FA code
+  await page.fill('input[type="tel"]', token);
+  await page.click('button:has-text("Next")');
+  // Step 6: Verify successful login (e.g., inbox loaded)
+  await page.waitForURL('https://mail.google.com/mail/**', { timeout: 20000 });
+  await expect(page.locator('div[aria-label="Google apps"]').first()).toBeVisible();
+  console.log('✅ Login successful!');
+});</t>
+  </si>
+  <si>
+    <t>import { test, expect, Page } from '@playwright/test';
+import { authenticator } from 'otpauth';
+import * as dotenv from 'dotenv';
+import { GmailLoginPage } from './pages/gmail-login.page';
+// Load environment variables
+dotenv.config();
+// Test data interface
+interface TestCredentials {
+  email: string;
+  password: string;
+  recoveryEmail?: string;
+}
+class TestData {
+  static readonly credentials: TestCredentials = {
+    email: process.env.GMAIL_EMAIL || '',
+    password: process.env.GMAIL_PASSWORD || '',
+    recoveryEmail: process.env.RECOVERY_EMAIL
+  };
+  static readonly twoFASecret: string = process.env.GMAIL_2FA_SECRET || '';
+  static readonly backupCodes: string[] = process.env.GMAIL_BACKUP_CODES?.split(',') || [];
+  static readonly phoneNumber: string = process.env.PHONE_NUMBER || '';
+}
+// Utility function to generate TOTP
+function generateTOTP(secret: string): string {
+  const totp = new authenticator.TOTP({
+    secret: secret.replace(/\s/g, ''),
+    algorithm: 'SHA1',
+    digits: 6,
+    period: 30
+  });
+  return totp.generate();
+}
+// Test Suite
+test.describe('Gmail Login with 2FA', () =&gt; {
+  let page: Page;
+  let gmailLoginPage: GmailLoginPage;
+  test.beforeAll(async ({ browser }) =&gt; {
+    page = await browser.newPage({
+      viewport: { width: 1280, height: 720 },
+      userAgent: 'Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36'
+    });
+    gmailLoginPage = new GmailLoginPage(page);
+  });
+  test.beforeEach(async () =&gt; {
+    // Navigate to Gmail
+await page.goto('https://mail.google.com');
+    await page.waitForTimeout(2000);
+  });
+  test.afterAll(async () =&gt; {
+    await page.close();
+  });
+  test('TC001: Successful login with TOTP 2FA', async () =&gt; {
+    console.log('Starting TOTP 2FA login test...');
+    // Step 1: Enter email
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await page.waitForTimeout(2000);
+    // Step 2: Enter password
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    await page.waitForTimeout(3000);
+    // Step 3: Handle 2FA - TOTP
+    const totpCode = generateTOTP(TestData.twoFASecret);
+    console.log(`Generated TOTP: ${totpCode}`);
+    await gmailLoginPage.enter2FACode(totpCode);
+    await page.waitForTimeout(5000);
+    // Verify successful login
+    const isLoggedIn = await gmailLoginPage.isLoggedIn();
+    expect(isLoggedIn).toBeTruthy();
+    // Capture screenshot for evidence
+    await page.screenshot({ path: 'screenshots/totp-login-success.png', fullPage: true });
+    console.log('TOTP 2FA login successful!');
+  });
+  test('TC002: Login with backup code', async () =&gt; {
+    console.log('Starting backup code login test...');
+    if (TestData.backupCodes.length === 0) {
+      console.warn('No backup codes available, skipping test');
+      return;
+    }
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await page.waitForTimeout(2000);
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    await page.waitForTimeout(3000);
+    // Click "Try another way" for backup code
+    await gmailLoginPage.tryAnotherWay();
+    await page.waitForTimeout(1000);
+    // Select backup code option
+    await gmailLoginPage.select2FAMethod('backup');
+    await page.waitForTimeout(2000);
+    // Use first backup code
+    const backupCode = TestData.backupCodes[0];
+    await gmailLoginPage.enterBackupCode(backupCode);
+    await page.waitForTimeout(5000);
+    const isLoggedIn = await gmailLoginPage.isLoggedIn();
+    expect(isLoggedIn).toBeTruthy();
+    await page.screenshot({ path: 'screenshots/backup-code-login.png', fullPage: true });
+    console.log('Backup code login successful!');
+  });
+  test('TC003: Login with SMS verification', async () =&gt; {
+    console.log('Starting SMS verification test...');
+    // Note: This test requires SMS capability
+    // For actual SMS, you'd need integration with SMS service
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await page.waitForTimeout(2000);
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    await page.waitForTimeout(3000);
+    await gmailLoginPage.tryAnotherWay();
+    await page.waitForTimeout(1000);
+    await gmailLoginPage.select2FAMethod('sms');
+    await page.waitForTimeout(2000);
+    // Verify SMS option is presented
+    const smsOptionVisible = await page.locator('text=Send a text message').isVisible();
+    expect(smsOptionVisible).toBeTruthy();
+    await page.screenshot({ path: 'screenshots/sms-option.png', fullPage: true });
+    console.log('SMS verification option available');
+  });
+  test('TC004: Invalid 2FA code should fail', async () =&gt; {
+    console.log('Testing invalid 2FA code...');
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await page.waitForTimeout(2000);
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    await page.waitForTimeout(3000);
+    // Enter invalid 2FA code
+    await gmailLoginPage.enter2FACode('000000');
+    await page.waitForTimeout(3000);
+    // Verify error message
+    const errorVisible = await page.locator('text=Try again|Wrong code|Invalid code').first().isVisible();
+    expect(errorVisible).toBeTruthy();
+    await page.screenshot({ path: 'screenshots/invalid-2fa-error.png' });
+    console.log('Invalid 2FA code properly rejected');
+  });
+  test('TC005: Remember this computer option', async () =&gt; {
+    console.log('Testing "Remember this computer" option...');
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await page.waitForTimeout(2000);
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    await page.waitForTimeout(3000);
+    // Generate and enter valid TOTP
+    const totpCode = generateTOTP(TestData.twoFASecret);
+    await gmailLoginPage.enter2FACode(totpCode);
+    // Check for "Don't ask again on this computer"
+    const rememberCheckbox = page.locator('input[type="checkbox"][name="trustDevice"]');
+    const isCheckboxVisible = await rememberCheckbox.isVisible();
+    if (isCheckboxVisible) {
+      await rememberCheckbox.check();
+      console.log('"Remember this computer" option selected');
+    }
+    await page.waitForTimeout(5000);
+    // Logout and login again to verify
+    await gmailLoginPage.logout();
+    await page.waitForTimeout(3000);
+    // Login again - should skip 2FA if remembered
+await page.goto('https://mail.google.com');
+await gmailLoginPage.enterEmail(TestData.credentials.email);
+    await gmailLoginPage.enterPassword(TestData.credentials.password);
+    // Should go directly to inbox if remembered
+    await page.waitForTimeout(5000);
+    const directAccess = await page.locator('a[aria-label*="Inbox"]').isVisible();
+    console.log(`Direct access after remembering: ${directAccess}`);
+    await page.screenshot({ path: 'screenshots/remember-computer.png' });
+  });
+});</t>
+  </si>
+  <si>
+    <t>Prompt 7</t>
   </si>
 </sst>
 </file>
@@ -382,7 +606,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,6 +622,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -444,6 +674,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,11 +1013,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14906783-2206-4AFB-8B51-CBCECD60AB61}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.109375" customWidth="1"/>
     <col min="2" max="2" width="32.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -895,12 +1131,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -908,7 +1144,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -916,7 +1152,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -924,12 +1160,12 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -937,370 +1173,608 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B35" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F31" t="s">
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B32">
+      <c r="B36" s="10">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B33">
+      <c r="B37" s="10">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B38" s="10">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D36" t="s">
+      <c r="C40" s="10"/>
+      <c r="D40" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B41" s="10">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B38">
+      <c r="B42" s="10">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B39">
+      <c r="B43" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D41" t="s">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B42">
+      <c r="B46" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B43">
+      <c r="B47" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B44">
+      <c r="B48" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D46" t="s">
+      <c r="C50" s="10"/>
+      <c r="D50" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B47">
+      <c r="B51" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B50">
+      <c r="B54" s="10">
         <v>13</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F52" t="s">
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B53">
+      <c r="B57" s="10">
         <v>15</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B56">
+      <c r="B60" s="10">
         <v>14</v>
       </c>
-      <c r="F56" t="s">
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+    <row r="70" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B70" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C70" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D70" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B71" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C71" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D71" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B72" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D72" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B73" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C73" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D73" s="7" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D78" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E74" s="5"/>
-    </row>
-    <row r="75" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
+      <c r="E78" s="5"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B79" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C79" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D79" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B80" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B81" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D81" s="7" t="s">
         <v>87</v>
       </c>
     </row>
